--- a/Input/Config.xlsx
+++ b/Input/Config.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>24334</v>
+        <v>23779.15</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13.2</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +637,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -660,10 +660,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>